--- a/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
+++ b/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1883D7FE-A36C-45E0-BD07-AC98EE527C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A31432-220A-4576-8F98-BE0C1393855E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>alpha_k</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>n</t>
+  </si>
+  <si>
+    <t>dPb/dt</t>
+  </si>
+  <si>
+    <t>Run Speed</t>
   </si>
 </sst>
 </file>
@@ -145,6 +151,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>var (Constant</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> dPb/dt)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -397,6 +433,569 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-CA"/>
+                  <a:t>Alpha</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228452624"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="228452624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228453104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>mu</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> (Constant dPb/dt)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1150</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>3.4205000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1262999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.7416999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.2782999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7504</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.1487999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4931999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.7747000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.0030000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.1958000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.3617999999999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.5994999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.7073999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.7840999999999996</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.8441999999999998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.8811</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.9526000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.9782000000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.0075000000000003</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.0663999999999998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.0678999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.1001999999999992</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.1443999999999992</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.1591000000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FA5E-4536-8C2F-DD6A3FDFA44B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="228453104"/>
+        <c:axId val="228452624"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="228453104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-CA"/>
+                  <a:t>Alpha</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -505,491 +1104,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>mu</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$26</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>250</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>350</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>450</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>550</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>600</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>650</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>700</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>850</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>900</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>950</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1000</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1050</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1150</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1200</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1250</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1350</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1400</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$26</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>3.4205000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.1262999999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.7416999999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.2782999999999998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.7504</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6.1487999999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6.4931999999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.7747000000000002</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.0030000000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.1958000000000002</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7.3617999999999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>7.5994999999999999</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7.7073999999999998</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>7.7840999999999996</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.8441999999999998</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.8811</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7.9526000000000003</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.9782000000000002</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8.0075000000000003</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8.0663999999999998</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.0678999999999998</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.1001999999999992</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>8.1443999999999992</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8.1591000000000005</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FA5E-4536-8C2F-DD6A3FDFA44B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="228453104"/>
-        <c:axId val="228452624"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="228453104"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="228452624"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="228452624"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="228453104"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2793,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -2804,9 +2918,10 @@
     <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2837,8 +2952,14 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2872,8 +2993,14 @@
       <c r="K2">
         <v>20000</v>
       </c>
+      <c r="L2">
+        <v>2.2847282667417322E-3</v>
+      </c>
+      <c r="M2">
+        <v>12.521185206834646</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2901,14 +3028,8 @@
       <c r="I3">
         <v>2.6997700000000002E-4</v>
       </c>
-      <c r="J3">
-        <v>50</v>
-      </c>
-      <c r="K3">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2936,14 +3057,8 @@
       <c r="I4">
         <v>7.3736500000000003E-4</v>
       </c>
-      <c r="J4">
-        <v>50</v>
-      </c>
-      <c r="K4">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2971,14 +3086,8 @@
       <c r="I5">
         <v>6.5837000000000003E-4</v>
       </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
-      <c r="K5">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3006,14 +3115,8 @@
       <c r="I6">
         <v>6.6518999999999997E-4</v>
       </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-      <c r="K6">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3041,14 +3144,8 @@
       <c r="I7">
         <v>8.7852399999999999E-4</v>
       </c>
-      <c r="J7">
-        <v>50</v>
-      </c>
-      <c r="K7">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3076,14 +3173,8 @@
       <c r="I8">
         <v>1.1395590000000001E-3</v>
       </c>
-      <c r="J8">
-        <v>50</v>
-      </c>
-      <c r="K8">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3111,14 +3202,8 @@
       <c r="I9">
         <v>1.4104460000000001E-3</v>
       </c>
-      <c r="J9">
-        <v>50</v>
-      </c>
-      <c r="K9">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3146,14 +3231,8 @@
       <c r="I10">
         <v>1.5769340000000001E-3</v>
       </c>
-      <c r="J10">
-        <v>50</v>
-      </c>
-      <c r="K10">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3181,14 +3260,8 @@
       <c r="I11">
         <v>1.686306E-3</v>
       </c>
-      <c r="J11">
-        <v>50</v>
-      </c>
-      <c r="K11">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3216,14 +3289,8 @@
       <c r="I12">
         <v>2.2256239999999998E-3</v>
       </c>
-      <c r="J12">
-        <v>50</v>
-      </c>
-      <c r="K12">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3251,14 +3318,8 @@
       <c r="I13">
         <v>2.202425E-3</v>
       </c>
-      <c r="J13">
-        <v>50</v>
-      </c>
-      <c r="K13">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3286,14 +3347,8 @@
       <c r="I14">
         <v>2.7696180000000002E-3</v>
       </c>
-      <c r="J14">
-        <v>50</v>
-      </c>
-      <c r="K14">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3321,14 +3376,8 @@
       <c r="I15">
         <v>3.0028920000000001E-3</v>
       </c>
-      <c r="J15">
-        <v>50</v>
-      </c>
-      <c r="K15">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3356,14 +3405,8 @@
       <c r="I16">
         <v>2.963266E-3</v>
       </c>
-      <c r="J16">
-        <v>50</v>
-      </c>
-      <c r="K16">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3391,14 +3434,8 @@
       <c r="I17">
         <v>3.3286050000000001E-3</v>
       </c>
-      <c r="J17">
-        <v>50</v>
-      </c>
-      <c r="K17">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3426,14 +3463,8 @@
       <c r="I18">
         <v>3.373067E-3</v>
       </c>
-      <c r="J18">
-        <v>50</v>
-      </c>
-      <c r="K18">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3461,14 +3492,8 @@
       <c r="I19">
         <v>4.2576960000000001E-3</v>
       </c>
-      <c r="J19">
-        <v>50</v>
-      </c>
-      <c r="K19">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3496,14 +3521,8 @@
       <c r="I20">
         <v>4.0670489999999997E-3</v>
       </c>
-      <c r="J20">
-        <v>50</v>
-      </c>
-      <c r="K20">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3531,14 +3550,8 @@
       <c r="I21">
         <v>4.4756750000000001E-3</v>
       </c>
-      <c r="J21">
-        <v>50</v>
-      </c>
-      <c r="K21">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3566,14 +3579,8 @@
       <c r="I22">
         <v>4.8595899999999996E-3</v>
       </c>
-      <c r="J22">
-        <v>50</v>
-      </c>
-      <c r="K22">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3601,14 +3608,8 @@
       <c r="I23">
         <v>5.7491870000000002E-3</v>
       </c>
-      <c r="J23">
-        <v>50</v>
-      </c>
-      <c r="K23">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3636,14 +3637,8 @@
       <c r="I24">
         <v>4.2134759999999999E-3</v>
       </c>
-      <c r="J24">
-        <v>50</v>
-      </c>
-      <c r="K24">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3671,14 +3666,8 @@
       <c r="I25">
         <v>6.9873950000000004E-3</v>
       </c>
-      <c r="J25">
-        <v>50</v>
-      </c>
-      <c r="K25">
-        <v>20000</v>
-      </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3705,12 +3694,6 @@
       </c>
       <c r="I26">
         <v>5.474133E-3</v>
-      </c>
-      <c r="J26">
-        <v>50</v>
-      </c>
-      <c r="K26">
-        <v>20000</v>
       </c>
     </row>
   </sheetData>

--- a/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
+++ b/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A31432-220A-4576-8F98-BE0C1393855E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1C2F82-242A-43A1-AA33-E8E9FCA20F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,10 +328,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$25</c:f>
+              <c:f>Sheet1!$E$2:$E$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0.3155</c:v>
                 </c:pt>
@@ -403,6 +403,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>3.1524000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.5017999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -922,7 +925,1012 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="228453104"/>
+        <c:axId val="228452624"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="228453104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-CA"/>
+                  <a:t>Alpha</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228452624"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="228452624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228453104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>dvar/dalpha (Constant dPb/dt)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1150</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2.2723E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6997700000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.3736500000000003E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5837000000000003E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.6518999999999997E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.7852399999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1395590000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4104460000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.5769340000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.686306E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.2256239999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.202425E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.7696180000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.0028920000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.963266E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.3286050000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.373067E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.2576960000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.0670489999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.4756750000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.8595899999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.7491870000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.2134759999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.9873950000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.474133E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-54C6-4962-860B-D4381FD1F624}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="228453104"/>
+        <c:axId val="228452624"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="228453104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-CA"/>
+                  <a:t>Alpha</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228452624"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="228452624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228453104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>dmu/dalpha (Constant dPb/dt)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1150</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$2:$H$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>1.4116235E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2307864E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0731114999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.4419759999999995E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.9684730000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.8888380000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.6283660000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.5661740000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.85623E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.3207319999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.7633290000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.9906239999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.1581270000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.534061E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2026789999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.3710400000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.4300440000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.1155099999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.86128E-4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.1787029999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.9774E-5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.44817E-4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.8520099999999996E-4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.92816E-4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.8836000000000003E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FE6F-4E37-91D2-BB784E49B9E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1228,6 +2236,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -2260,19 +3348,1051 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>80962</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2301,15 +4421,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2331,6 +4451,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36C97A95-B44B-4703-95D8-C01543FCA144}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC970F36-7F83-4870-8301-59552A218445}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2905,6 +5101,568 @@
 </a:themeOverride>
 </file>
 
+<file path=xl/theme/themeOverride2.xml><?xml version="1.0" encoding="utf-8"?>
+<a:themeOverride xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <a:clrScheme name="Office 2007 - 2010">
+    <a:dk1>
+      <a:sysClr val="windowText" lastClr="000000"/>
+    </a:dk1>
+    <a:lt1>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:lt1>
+    <a:dk2>
+      <a:srgbClr val="1F497D"/>
+    </a:dk2>
+    <a:lt2>
+      <a:srgbClr val="EEECE1"/>
+    </a:lt2>
+    <a:accent1>
+      <a:srgbClr val="4F81BD"/>
+    </a:accent1>
+    <a:accent2>
+      <a:srgbClr val="C0504D"/>
+    </a:accent2>
+    <a:accent3>
+      <a:srgbClr val="9BBB59"/>
+    </a:accent3>
+    <a:accent4>
+      <a:srgbClr val="8064A2"/>
+    </a:accent4>
+    <a:accent5>
+      <a:srgbClr val="4BACC6"/>
+    </a:accent5>
+    <a:accent6>
+      <a:srgbClr val="F79646"/>
+    </a:accent6>
+    <a:hlink>
+      <a:srgbClr val="0000FF"/>
+    </a:hlink>
+    <a:folHlink>
+      <a:srgbClr val="800080"/>
+    </a:folHlink>
+  </a:clrScheme>
+  <a:fontScheme name="Office 2007 - 2010">
+    <a:majorFont>
+      <a:latin typeface="Cambria"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Times New Roman"/>
+      <a:font script="Hebr" typeface="Times New Roman"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="MoolBoran"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Times New Roman"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:majorFont>
+    <a:minorFont>
+      <a:latin typeface="Calibri"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Arial"/>
+      <a:font script="Hebr" typeface="Arial"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="DaunPenh"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Arial"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:minorFont>
+  </a:fontScheme>
+  <a:fmtScheme name="Office 2007 - 2010">
+    <a:fillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="50000"/>
+              <a:satMod val="300000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="35000">
+            <a:schemeClr val="phClr">
+              <a:tint val="37000"/>
+              <a:satMod val="300000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:tint val="15000"/>
+              <a:satMod val="350000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="16200000" scaled="1"/>
+      </a:gradFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:shade val="51000"/>
+              <a:satMod val="130000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="80000">
+            <a:schemeClr val="phClr">
+              <a:shade val="93000"/>
+              <a:satMod val="130000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="94000"/>
+              <a:satMod val="135000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="16200000" scaled="0"/>
+      </a:gradFill>
+    </a:fillStyleLst>
+    <a:lnStyleLst>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+            <a:satMod val="105000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+      </a:ln>
+      <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+      </a:ln>
+      <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+      </a:ln>
+    </a:lnStyleLst>
+    <a:effectStyleLst>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="38000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="35000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="35000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="threePt" dir="t">
+            <a:rot lat="0" lon="0" rev="1200000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="63500" h="25400"/>
+        </a:sp3d>
+      </a:effectStyle>
+    </a:effectStyleLst>
+    <a:bgFillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="40000"/>
+              <a:satMod val="350000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="40000">
+            <a:schemeClr val="phClr">
+              <a:tint val="45000"/>
+              <a:shade val="99000"/>
+              <a:satMod val="350000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="20000"/>
+              <a:satMod val="255000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+      </a:gradFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="80000"/>
+              <a:satMod val="300000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="30000"/>
+              <a:satMod val="200000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+    </a:bgFillStyleLst>
+  </a:fmtScheme>
+</a:themeOverride>
+</file>
+
+<file path=xl/theme/themeOverride3.xml><?xml version="1.0" encoding="utf-8"?>
+<a:themeOverride xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <a:clrScheme name="Office 2007 - 2010">
+    <a:dk1>
+      <a:sysClr val="windowText" lastClr="000000"/>
+    </a:dk1>
+    <a:lt1>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:lt1>
+    <a:dk2>
+      <a:srgbClr val="1F497D"/>
+    </a:dk2>
+    <a:lt2>
+      <a:srgbClr val="EEECE1"/>
+    </a:lt2>
+    <a:accent1>
+      <a:srgbClr val="4F81BD"/>
+    </a:accent1>
+    <a:accent2>
+      <a:srgbClr val="C0504D"/>
+    </a:accent2>
+    <a:accent3>
+      <a:srgbClr val="9BBB59"/>
+    </a:accent3>
+    <a:accent4>
+      <a:srgbClr val="8064A2"/>
+    </a:accent4>
+    <a:accent5>
+      <a:srgbClr val="4BACC6"/>
+    </a:accent5>
+    <a:accent6>
+      <a:srgbClr val="F79646"/>
+    </a:accent6>
+    <a:hlink>
+      <a:srgbClr val="0000FF"/>
+    </a:hlink>
+    <a:folHlink>
+      <a:srgbClr val="800080"/>
+    </a:folHlink>
+  </a:clrScheme>
+  <a:fontScheme name="Office 2007 - 2010">
+    <a:majorFont>
+      <a:latin typeface="Cambria"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Times New Roman"/>
+      <a:font script="Hebr" typeface="Times New Roman"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="MoolBoran"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Times New Roman"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:majorFont>
+    <a:minorFont>
+      <a:latin typeface="Calibri"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Arial"/>
+      <a:font script="Hebr" typeface="Arial"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="DaunPenh"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Arial"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:minorFont>
+  </a:fontScheme>
+  <a:fmtScheme name="Office 2007 - 2010">
+    <a:fillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="50000"/>
+              <a:satMod val="300000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="35000">
+            <a:schemeClr val="phClr">
+              <a:tint val="37000"/>
+              <a:satMod val="300000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:tint val="15000"/>
+              <a:satMod val="350000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="16200000" scaled="1"/>
+      </a:gradFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:shade val="51000"/>
+              <a:satMod val="130000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="80000">
+            <a:schemeClr val="phClr">
+              <a:shade val="93000"/>
+              <a:satMod val="130000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="94000"/>
+              <a:satMod val="135000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="16200000" scaled="0"/>
+      </a:gradFill>
+    </a:fillStyleLst>
+    <a:lnStyleLst>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+            <a:satMod val="105000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+      </a:ln>
+      <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+      </a:ln>
+      <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+      </a:ln>
+    </a:lnStyleLst>
+    <a:effectStyleLst>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="38000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="35000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="35000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="threePt" dir="t">
+            <a:rot lat="0" lon="0" rev="1200000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="63500" h="25400"/>
+        </a:sp3d>
+      </a:effectStyle>
+    </a:effectStyleLst>
+    <a:bgFillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="40000"/>
+              <a:satMod val="350000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="40000">
+            <a:schemeClr val="phClr">
+              <a:tint val="45000"/>
+              <a:shade val="99000"/>
+              <a:satMod val="350000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="20000"/>
+              <a:satMod val="255000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+      </a:gradFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="80000"/>
+              <a:satMod val="300000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="30000"/>
+              <a:satMod val="200000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+    </a:bgFillStyleLst>
+  </a:fmtScheme>
+</a:themeOverride>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M26"/>

--- a/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
+++ b/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1C2F82-242A-43A1-AA33-E8E9FCA20F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95B3F02-E9B0-4333-99B3-6DB4A5BCE0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -678,8 +678,22 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>mu</a:t>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>v(</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" baseline="0">
+                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>α</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>)</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
@@ -1689,7 +1703,15 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t>dmu/dalpha (Constant dPb/dt)</a:t>
+              <a:t>dv/d</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" baseline="0"/>
+              <a:t>α</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> (Constant dPb/dt)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4385,15 +4407,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>80962</xdr:rowOff>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4421,15 +4443,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
+      <xdr:colOff>295275</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
+      <xdr:colOff>600075</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4459,15 +4481,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4497,15 +4519,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
+++ b/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95B3F02-E9B0-4333-99B3-6DB4A5BCE0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99672ED6-E2CB-4D34-80D4-AF7AECC1B7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1013,7 +1013,7 @@
           </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>

--- a/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
+++ b/DDM GD Find Alpha Rebuild/Deme_51_alpha_w_const_Rtroc_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99672ED6-E2CB-4D34-80D4-AF7AECC1B7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531E52CC-B949-4407-B6C6-CDE5228166D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,14 +170,39 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>var (Constant</a:t>
+              <a:rPr lang="en-US" sz="1400">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>var(</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="el-GR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>α</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>) (Constant</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" baseline="0">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
               <a:t> dPb/dt)</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-US" sz="1400">
+              <a:latin typeface="+mn-lt"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -678,26 +703,29 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US" sz="1400" baseline="0">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
               <a:t>v(</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="el-GR" baseline="0">
-                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:rPr lang="el-GR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>α</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0">
-                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              <a:rPr lang="en-US" sz="1400" baseline="0">
+                <a:latin typeface="+mn-lt"/>
               </a:rPr>
-              <a:t>)</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> (Constant dPb/dt)</a:t>
+              <a:t>) (Constant dPb/dt)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1199,8 +1227,29 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t>dvar/dalpha (Constant dPb/dt)</a:t>
+              <a:rPr lang="en-US" sz="1400" baseline="0">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>dvar/d</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>α</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" baseline="0">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> (Constant dPb/dt)</a:t>
             </a:r>
           </a:p>
         </c:rich>
